--- a/NORMAL DISTRIBUTION.xlsx
+++ b/NORMAL DISTRIBUTION.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4662F097-2613-42FB-BF92-5511BE6D5787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CF0484-30E0-4615-9F45-F8E90FF2BA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAAEAF96-EE2B-4401-8C74-4AF877A2D578}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{EAAEAF96-EE2B-4401-8C74-4AF877A2D578}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CONTINUS NORMAL DISTRIBUTION" sheetId="1" r:id="rId1"/>
+    <sheet name="COVARIANCE" sheetId="2" r:id="rId2"/>
+    <sheet name="CORRELATION " sheetId="3" r:id="rId3"/>
+    <sheet name="MEAN ,MEDIAN,MAD ,QUARTILE ,IQR" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>X = 115</t>
   </si>
@@ -82,6 +85,51 @@
   </si>
   <si>
     <t>50&lt;X&lt;80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA -1 </t>
+  </si>
+  <si>
+    <t>DATA -2</t>
+  </si>
+  <si>
+    <t>FOR FINDING TWO COLUNMS VARIANCE</t>
+  </si>
+  <si>
+    <t>DO COLUMNS  KA CORRELATION CHEK KARNE KE LIYE USE HOTA HAI</t>
+  </si>
+  <si>
+    <t>DATA - 1</t>
+  </si>
+  <si>
+    <t>DATA - 2</t>
+  </si>
+  <si>
+    <t>CORRELATION</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>MEDIAN</t>
+  </si>
+  <si>
+    <t>VAR</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q0</t>
+  </si>
+  <si>
+    <t>IQR</t>
   </si>
 </sst>
 </file>
@@ -97,12 +145,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,12 +186,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,14 +514,14 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
@@ -472,10 +530,10 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <f>_xlfn.NORM.DIST(115,100,10,0)</f>
         <v>1.2951759566589173E-2</v>
       </c>
@@ -485,10 +543,10 @@
       <c r="J4">
         <v>70</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <f>_xlfn.NORM.DIST(85,70,10,1)</f>
         <v>0.93319279873114191</v>
       </c>
@@ -500,10 +558,10 @@
       <c r="C5">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <f>_xlfn.NORM.DIST(78,100,10,0)</f>
         <v>3.5474592846231421E-3</v>
       </c>
@@ -513,69 +571,69 @@
       <c r="J5">
         <v>10</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <f>_xlfn.NORM.DIST(90,70,10,1)-_xlfn.NORM.DIST(70,70,10,1)</f>
         <v>0.47724986805182079</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <f>_xlfn.NORM.DIST(80,100,10,1)</f>
         <v>2.2750131948179191E-2</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <f>_xlfn.NORM.DIST(95,70,10,1)</f>
         <v>0.99379033467422384</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <f>1-E6</f>
         <v>0.97724986805182079</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <f>_xlfn.NORM.DIST(80,70,10,1)-_xlfn.NORM.DIST(50,70,10,1)</f>
         <v>0.81859461412036383</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <f>1-_xlfn.NORM.DIST(125,100,10,1)</f>
         <v>6.2096653257761592E-3</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <f>0.5-_xlfn.NORM.DIST(85,100,10,1)</f>
         <v>0.43319279873114191</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <f>_xlfn.NORM.DIST(125,100,10,1)-_xlfn.NORM.DIST(95,100,10,1)</f>
         <v>0.68525279594823696</v>
       </c>
@@ -586,4 +644,453 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A3E50F-AEBA-4067-A30D-57FC137C386F}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <f ca="1">RANDBETWEEN(10,20)</f>
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <f ca="1">RANDBETWEEN(100,200)</f>
+        <v>164</v>
+      </c>
+      <c r="D2">
+        <f ca="1">_xlfn.COVARIANCE.P(A2:A14,B2:B14)</f>
+        <v>7.5857988165680457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f t="shared" ref="A3:A14" ca="1" si="0">RANDBETWEEN(10,20)</f>
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B14" ca="1" si="1">RANDBETWEEN(100,200)</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ca="1" si="1"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <f t="shared" ca="1" si="1"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <f t="shared" ca="1" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <f t="shared" ca="1" si="1"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <f t="shared" ca="1" si="1"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <f t="shared" ca="1" si="1"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <f t="shared" ca="1" si="1"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <f t="shared" ca="1" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ca="1" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ca="1" si="1"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <f t="shared" ca="1" si="1"/>
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0678B5-BB95-42B6-9874-AF0F08FDE3F4}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3">
+        <f>CORREL(A3:A12,B3:B12)</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FCA3C05-2B35-4660-94DD-1C20ECD3AC67}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1">
+        <f ca="1">QUARTILE(A2:A17,0)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <f ca="1">RANDBETWEEN(10,50)</f>
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <f ca="1">AVERAGE(A2:A17)</f>
+        <v>31.4375</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2">
+        <f ca="1">QUARTILE(A3:A18,1)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f t="shared" ref="A3:A17" ca="1" si="0">RANDBETWEEN(10,50)</f>
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <f ca="1">MEDIAN(A2:A17)</f>
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3">
+        <f ca="1">QUARTILE(A4:A19,2)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <f ca="1">_xlfn.VAR.P(A2:A17)</f>
+        <v>92.12109375</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <f ca="1">QUARTILE(A5:A20,3)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <f ca="1">_xlfn.STDEV.P(A2:A17)</f>
+        <v>9.5979734189046386</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <f ca="1">G4-G2</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/NORMAL DISTRIBUTION.xlsx
+++ b/NORMAL DISTRIBUTION.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CF0484-30E0-4615-9F45-F8E90FF2BA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96890B31-FE5F-49EF-BE7A-2363CBF741F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{EAAEAF96-EE2B-4401-8C74-4AF877A2D578}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{EAAEAF96-EE2B-4401-8C74-4AF877A2D578}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTINUS NORMAL DISTRIBUTION" sheetId="1" r:id="rId1"/>
     <sheet name="COVARIANCE" sheetId="2" r:id="rId2"/>
     <sheet name="CORRELATION " sheetId="3" r:id="rId3"/>
     <sheet name="MEAN ,MEDIAN,MAD ,QUARTILE ,IQR" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
   <si>
     <t>X = 115</t>
   </si>
@@ -130,6 +131,48 @@
   </si>
   <si>
     <t>IQR</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>H0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P VALUE </t>
+  </si>
+  <si>
+    <t>ALPHA VALUE</t>
+  </si>
+  <si>
+    <t>T-STAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCLUSION :  </t>
+  </si>
+  <si>
+    <t>HERE  OUR P VALUE IS LESS THAN SIGNIFICANT LEVEL (ALPHA), SO WE REJECT NULL HYPOTHYSIS  AND WE CONCLUDE THAT SAMPLE MEAN IS SIGNIFICANTLY DIFFERENT FROM POPULATION MEAN</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>IS 70</t>
+  </si>
+  <si>
+    <t>NOT 70</t>
+  </si>
+  <si>
+    <t>T-CRIT</t>
+  </si>
+  <si>
+    <t>NO SIGNIFICANT DIFFRENCE IN TWO SAMPLE</t>
+  </si>
+  <si>
+    <t>THRE IS A SIGNIFICANT DIFFRENCE IN TWO SAMPLE</t>
+  </si>
+  <si>
+    <t>HERE  OUR P VALUE IS LESS THAN SIGNIFICANT LEVEL (ALPHA), SO WE REJECT NULL HYPOTHYSIS  AND WE CONCLUDE THAT SAMPLE 1  MEAN IS SIGNIFICANTLY DIFFERENT FROM SAMPLE 2  MEAN</t>
   </si>
 </sst>
 </file>
@@ -186,16 +229,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,14 +558,14 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
@@ -661,142 +705,142 @@
       <c r="B1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <f ca="1">RANDBETWEEN(10,20)</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <f ca="1">RANDBETWEEN(100,200)</f>
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="D2">
         <f ca="1">_xlfn.COVARIANCE.P(A2:A14,B2:B14)</f>
-        <v>7.5857988165680457</v>
+        <v>26.869822485207099</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" ref="A3:A14" ca="1" si="0">RANDBETWEEN(10,20)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B14" ca="1" si="1">RANDBETWEEN(100,200)</f>
-        <v>103</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="1"/>
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="1"/>
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>147</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>165</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>107</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>109</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +880,7 @@
       <c r="B3" s="1">
         <v>10</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>CORREL(A3:A12,B3:B12)</f>
         <v>-1</v>
       </c>
@@ -935,159 +979,394 @@
       </c>
       <c r="G1">
         <f ca="1">QUARTILE(A2:A17,0)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <f ca="1">RANDBETWEEN(10,50)</f>
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2">
         <f ca="1">AVERAGE(A2:A17)</f>
-        <v>31.4375</v>
+        <v>32.9375</v>
       </c>
       <c r="F2" t="s">
         <v>26</v>
       </c>
       <c r="G2">
         <f ca="1">QUARTILE(A3:A18,1)</f>
-        <v>25</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" ref="A3:A17" ca="1" si="0">RANDBETWEEN(10,50)</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3">
         <f ca="1">MEDIAN(A2:A17)</f>
-        <v>33</v>
+        <v>35.5</v>
       </c>
       <c r="F3" t="s">
         <v>27</v>
       </c>
       <c r="G3">
         <f ca="1">QUARTILE(A4:A19,2)</f>
-        <v>32</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4">
         <f ca="1">_xlfn.VAR.P(A2:A17)</f>
-        <v>92.12109375</v>
+        <v>201.30859375</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4">
         <f ca="1">QUARTILE(A5:A20,3)</f>
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5">
         <f ca="1">_xlfn.STDEV.P(A2:A17)</f>
-        <v>9.5979734189046386</v>
+        <v>14.188325967146371</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
       </c>
       <c r="G5">
         <f ca="1">G4-G2</f>
-        <v>13</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AACDDD2-345C-44E2-B3A7-C6C33A73B8A3}">
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="165.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <f ca="1">RANDBETWEEN(70,80)</f>
+        <v>70</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f t="shared" ref="A3:A11" ca="1" si="0">RANDBETWEEN(70,80)</f>
+        <v>71</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ca="1" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" ca="1" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" ca="1" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" ca="1" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" ca="1" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" ca="1" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" ca="1" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2.44</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" ca="1" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>85</v>
+      </c>
+      <c r="B21">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>87</v>
+      </c>
+      <c r="B22">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>90</v>
+      </c>
+      <c r="B23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>88</v>
+      </c>
+      <c r="B24">
+        <v>82</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>87</v>
+      </c>
+      <c r="B25">
+        <v>76</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2.306</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="1">
+        <v>5.79</v>
       </c>
     </row>
   </sheetData>

--- a/NORMAL DISTRIBUTION.xlsx
+++ b/NORMAL DISTRIBUTION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96890B31-FE5F-49EF-BE7A-2363CBF741F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D6DE1B-9D49-4FFB-B54C-F006C89E8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{EAAEAF96-EE2B-4401-8C74-4AF877A2D578}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{EAAEAF96-EE2B-4401-8C74-4AF877A2D578}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTINUS NORMAL DISTRIBUTION" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="CORRELATION " sheetId="3" r:id="rId3"/>
     <sheet name="MEAN ,MEDIAN,MAD ,QUARTILE ,IQR" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="confidence level " sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
   <si>
     <t>X = 115</t>
   </si>
@@ -173,13 +174,85 @@
   </si>
   <si>
     <t>HERE  OUR P VALUE IS LESS THAN SIGNIFICANT LEVEL (ALPHA), SO WE REJECT NULL HYPOTHYSIS  AND WE CONCLUDE THAT SAMPLE 1  MEAN IS SIGNIFICANTLY DIFFERENT FROM SAMPLE 2  MEAN</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>Sample Variance</t>
+  </si>
+  <si>
+    <t>Kurtosis</t>
+  </si>
+  <si>
+    <t>Skewness</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Confidence Level(95.0%)</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BY FORMULA </t>
+  </si>
+  <si>
+    <t>BY   DTA ANALYSIS</t>
+  </si>
+  <si>
+    <t>&lt;30,POP VAR UNKNOWN</t>
+  </si>
+  <si>
+    <t>&gt;30, PO VAR KNOWN</t>
+  </si>
+  <si>
+    <t>LOWER RANGE</t>
+  </si>
+  <si>
+    <t>UPPER RANGE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,8 +260,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,8 +282,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -225,11 +312,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -239,7 +346,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,35 +827,35 @@
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <f ca="1">RANDBETWEEN(10,20)</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <f ca="1">RANDBETWEEN(100,200)</f>
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D2">
         <f ca="1">_xlfn.COVARIANCE.P(A2:A14,B2:B14)</f>
-        <v>26.869822485207099</v>
+        <v>11.538461538461538</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" ref="A3:A14" ca="1" si="0">RANDBETWEEN(10,20)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B14" ca="1" si="1">RANDBETWEEN(100,200)</f>
-        <v>181</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -750,97 +865,97 @@
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="1"/>
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="1"/>
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="1"/>
-        <v>176</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="1"/>
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>102</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>106</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="1"/>
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -979,159 +1094,159 @@
       </c>
       <c r="G1">
         <f ca="1">QUARTILE(A2:A17,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <f ca="1">RANDBETWEEN(10,50)</f>
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2">
         <f ca="1">AVERAGE(A2:A17)</f>
-        <v>32.9375</v>
+        <v>30.25</v>
       </c>
       <c r="F2" t="s">
         <v>26</v>
       </c>
       <c r="G2">
         <f ca="1">QUARTILE(A3:A18,1)</f>
-        <v>24.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" ref="A3:A17" ca="1" si="0">RANDBETWEEN(10,50)</f>
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3">
         <f ca="1">MEDIAN(A2:A17)</f>
-        <v>35.5</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
         <v>27</v>
       </c>
       <c r="G3">
         <f ca="1">QUARTILE(A4:A19,2)</f>
-        <v>35.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4">
         <f ca="1">_xlfn.VAR.P(A2:A17)</f>
-        <v>201.30859375</v>
+        <v>166.1875</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4">
         <f ca="1">QUARTILE(A5:A20,3)</f>
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5">
         <f ca="1">_xlfn.STDEV.P(A2:A17)</f>
-        <v>14.188325967146371</v>
+        <v>12.891373084353738</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
       </c>
       <c r="G5">
         <f ca="1">G4-G2</f>
-        <v>21.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1157,7 +1272,7 @@
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <f ca="1">RANDBETWEEN(70,80)</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1166,7 +1281,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" ref="A3:A11" ca="1" si="0">RANDBETWEEN(70,80)</f>
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1181,7 +1296,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1196,13 +1311,13 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>33</v>
@@ -1236,7 +1351,7 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1251,12 +1366,11 @@
       <c r="K9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I10" s="1">
         <v>2.44</v>
@@ -1271,7 +1385,7 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1372,4 +1486,342 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F734E415-55A8-47DF-A352-C439587CCE85}">
+  <dimension ref="A3:M30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="L3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="7"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="1">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5">
+        <f ca="1">_xlfn.CONFIDENCE.T(0.05,E7,E5)</f>
+        <v>1.0758700219972479</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f ca="1">RANDBETWEEN(11,20)</f>
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1">
+        <f ca="1">AVERAGE(A6:$A$30)</f>
+        <v>15.28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6">
+        <f ca="1">_xlfn.CONFIDENCE.NORM(0.05,E7,25)</f>
+        <v>1.0216909563121077</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="5">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" ref="A7:A30" ca="1" si="0">RANDBETWEEN(11,20)</f>
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1">
+        <f ca="1">_xlfn.STDEV.S(A6:$A$30)</f>
+        <v>2.6064023736432813</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.55075705472861025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10" s="5">
+        <v>2.753785273643051</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11">
+        <f ca="1">E6-H5</f>
+        <v>14.204129978002751</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="5">
+        <v>7.583333333333333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12">
+        <f ca="1">E6+H5</f>
+        <v>16.355870021997248</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="5">
+        <v>-0.90907849914061067</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="5">
+        <v>-5.7255160758920898E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="5">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1.1367066930608665</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="L3:M3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>